--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484886_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484886_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4333</v>
+        <v>2.6244</v>
       </c>
       <c r="E2" t="n">
-        <v>2.373</v>
+        <v>3.1726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0603</v>
+        <v>-0.5482</v>
       </c>
       <c r="G2" t="n">
         <v>2.4211</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8258</v>
+        <v>-0.6347</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0582</v>
+        <v>-0.2586</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2323</v>
+        <v>-0.3761</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2942</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6183</v>
+        <v>1.4587</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6044</v>
+        <v>3.3653</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.986</v>
+        <v>-1.9067</v>
       </c>
       <c r="G3" t="n">
         <v>3.455</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5989</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9994</v>
+        <v>-0.2384</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5995</v>
+        <v>-0.5202</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1055</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4404</v>
+        <v>0.2632</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6994</v>
+        <v>-0.7179</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1398</v>
+        <v>0.9811</v>
       </c>
       <c r="G4" t="n">
         <v>-0.929</v>
@@ -766,13 +766,13 @@
         <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5326</v>
+        <v>-0.7098</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3963</v>
+        <v>-0.4148</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1363</v>
+        <v>-0.295</v>
       </c>
       <c r="V4" t="n">
         <v>1.7133</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0681</v>
+        <v>-1.3382</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3493</v>
+        <v>-1.2099</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7189</v>
+        <v>-0.1283</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6261</v>
+        <v>-2.3592</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5157</v>
+        <v>-1.818</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1103</v>
+        <v>-0.5412</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0623</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0211</v>
+        <v>-0.353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>-0.5417</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6883</v>
+        <v>-1.4645</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5369</v>
+        <v>-1.465</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1515</v>
+        <v>0.0005</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5661</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="S5" t="n">
-        <v>0.124</v>
+        <v>-1.4205</v>
       </c>
       <c r="T5" t="n">
-        <v>0.532</v>
+        <v>-0.5788</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.408</v>
+        <v>-0.8417</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8754</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1506</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3729</v>
+        <v>-1.3785</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9542</v>
+        <v>-0.739</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.327</v>
+        <v>-0.6395</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1958</v>
+        <v>-0.6261</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3021</v>
+        <v>-0.5157</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4979</v>
+        <v>-0.1103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7467</v>
+        <v>0.0623</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8813</v>
+        <v>0.0211</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1346</v>
+        <v>0.0411</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9425</v>
+        <v>-0.6883</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5792</v>
+        <v>-0.5369</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3633</v>
+        <v>-0.1515</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0041</v>
+        <v>-0.1863</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8492</v>
+        <v>0.1422</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.8452</v>
+        <v>-0.3286</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6302</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2661</v>
+        <v>-1.6148</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6514</v>
+        <v>1.2762</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9174</v>
+        <v>-2.891</v>
       </c>
       <c r="G7" t="n">
         <v>-3.9162</v>
@@ -1000,13 +1000,13 @@
         <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.693</v>
+        <v>-1.0417</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6902</v>
+        <v>-0.0653</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0028</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>2.777</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3431</v>
+        <v>-2.2709</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0297</v>
+        <v>0.4741</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3135</v>
+        <v>-2.745</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3592</v>
+        <v>-2.1958</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.818</v>
+        <v>0.3021</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5412</v>
+        <v>-2.4979</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8947000000000001</v>
+        <v>0.7467</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.353</v>
+        <v>1.8813</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5417</v>
+        <v>-1.1346</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4645</v>
+        <v>-2.9425</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.465</v>
+        <v>-1.5792</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0005</v>
+        <v>-1.3633</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4254</v>
+        <v>-0.894</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3986</v>
+        <v>0.3692</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0269</v>
+        <v>-1.2632</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8754</v>
+        <v>0.6302</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1506</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2752</v>
+        <v>-0.615</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2388</v>
+        <v>-4.3652</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4995</v>
+        <v>-2.4407</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7393</v>
+        <v>-1.9245</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1619</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.141</v>
+        <v>-1.2674</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4551</v>
+        <v>-0.3963</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6859</v>
+        <v>-0.8711</v>
       </c>
       <c r="V9" t="n">
         <v>0.951</v>
@@ -1189,16 +1189,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.797000000000001</v>
+        <v>-6.621300000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.005100000000001</v>
+        <v>3.180700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.802</v>
+        <v>-9.802099999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.312100000000001</v>
+        <v>-6.3121</v>
       </c>
       <c r="H10" t="n">
         <v>-5.4468</v>
@@ -1210,7 +1210,7 @@
         <v>10.4353</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4327</v>
+        <v>6.432699999999999</v>
       </c>
       <c r="L10" t="n">
         <v>4.002599999999999</v>
@@ -1225,7 +1225,7 @@
         <v>-4.8677</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9435</v>
+        <v>-0.9434999999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>-14.1525</v>
@@ -1234,13 +1234,13 @@
         <v>13.209</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.0886</v>
+        <v>-6.913</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.6166</v>
+        <v>-1.4408</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.4723</v>
+        <v>-5.4722</v>
       </c>
       <c r="V10" t="n">
         <v>7.5472</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.3491</v>
+        <v>7.568</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0036</v>
+        <v>6.1985</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3455</v>
+        <v>1.3696</v>
       </c>
       <c r="G11" t="n">
         <v>5.302</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6131</v>
+        <v>0.8321</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2409</v>
+        <v>0.4358</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3722</v>
+        <v>0.3963</v>
       </c>
       <c r="V11" t="n">
         <v>1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9292</v>
+        <v>3.1678</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1764</v>
+        <v>3.4943</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2472</v>
+        <v>-0.3265</v>
       </c>
       <c r="G12" t="n">
         <v>4.4079</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7289</v>
+        <v>0.9674</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4319</v>
+        <v>0.7499</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2969</v>
+        <v>0.2176</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2076</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8287</v>
+        <v>1.7727</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7435</v>
+        <v>2.7692</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>2.0625</v>
@@ -1468,13 +1468,13 @@
         <v>0.5661</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4078</v>
+        <v>1.3517</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9051</v>
+        <v>0.9308</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5027</v>
+        <v>0.421</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2642</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2335</v>
+        <v>1.3839</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8041</v>
+        <v>1.9015</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5705</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.8187</v>
@@ -1546,13 +1546,13 @@
         <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.472</v>
+        <v>-0.3217</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3545</v>
+        <v>-0.3016</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3018</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9113</v>
+        <v>1.2914</v>
       </c>
       <c r="E15" t="n">
-        <v>2.268</v>
+        <v>0.4123</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3567</v>
+        <v>0.8792</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5014</v>
+        <v>-1.2058</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5752</v>
+        <v>-1.0322</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0737</v>
+        <v>-0.1736</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5438</v>
+        <v>0.3282</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2106</v>
+        <v>-0.3639</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3332</v>
+        <v>0.6922</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0424</v>
+        <v>-1.534</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6354</v>
+        <v>-0.6683</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4069</v>
+        <v>-0.8657</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.887</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7682</v>
+        <v>0.6294</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6112</v>
+        <v>0.1032</v>
       </c>
       <c r="U15" t="n">
-        <v>0.157</v>
+        <v>0.5262</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.547</v>
+        <v>1.8678</v>
       </c>
       <c r="W15" t="n">
+        <v>1.8678</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9101</v>
+        <v>0.9666</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07489999999999999</v>
+        <v>2.3735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.985</v>
+        <v>-1.4069</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2058</v>
+        <v>0.6194</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0322</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1736</v>
+        <v>-0.1906</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3282</v>
+        <v>1.795</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3639</v>
+        <v>1.1199</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6922</v>
+        <v>0.6751</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.534</v>
+        <v>-1.1756</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6683</v>
+        <v>-0.3099</v>
       </c>
       <c r="O16" t="n">
         <v>-0.8657</v>
       </c>
       <c r="P16" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.887</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2481</v>
+        <v>0.4037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3839</v>
+        <v>0.2767</v>
       </c>
       <c r="U16" t="n">
-        <v>0.632</v>
+        <v>0.127</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8678</v>
+        <v>-0.6226</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8678</v>
+        <v>0.3018</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7393</v>
+        <v>0.8601</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2761</v>
+        <v>-0.7693</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5368</v>
+        <v>1.6295</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6194</v>
+        <v>0.286</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.087</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1906</v>
+        <v>-0.801</v>
       </c>
       <c r="J17" t="n">
-        <v>1.795</v>
+        <v>0.4007</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1199</v>
+        <v>1.5268</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6751</v>
+        <v>-1.1261</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1756</v>
+        <v>-0.1148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3099</v>
+        <v>-0.4398</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8657</v>
+        <v>0.325</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q17" t="n">
+        <v>-1.887</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5096</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.7359</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.5661</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.1764</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.1793</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.0029</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.6226</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.3018</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.9244</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.083</v>
+        <v>0.5203</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5488</v>
+        <v>1.586</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6318</v>
+        <v>-1.0657</v>
       </c>
       <c r="G18" t="n">
-        <v>0.286</v>
+        <v>0.5014</v>
       </c>
       <c r="H18" t="n">
-        <v>1.087</v>
+        <v>0.5752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.801</v>
+        <v>-0.0737</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4007</v>
+        <v>2.5438</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5268</v>
+        <v>1.2106</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1261</v>
+        <v>1.3332</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1148</v>
+        <v>-2.0424</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4398</v>
+        <v>-0.6354</v>
       </c>
       <c r="O18" t="n">
-        <v>0.325</v>
+        <v>-1.4069</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1934</v>
+        <v>1.3771</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0436</v>
+        <v>0.9292</v>
       </c>
       <c r="U18" t="n">
-        <v>0.237</v>
+        <v>0.448</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.019</v>
+        <v>-1.547</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1039</v>
+        <v>-0.0774</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3131</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2093</v>
+        <v>1.2357</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1276</v>
@@ -1936,13 +1936,13 @@
         <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1745</v>
+        <v>1.201</v>
       </c>
       <c r="T19" t="n">
         <v>0.9123</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2622</v>
+        <v>0.2887</v>
       </c>
       <c r="V19" t="n">
         <v>0.6606</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5545</v>
+        <v>-3.1744</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4732</v>
+        <v>-2.2783</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0813</v>
+        <v>-0.8961</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9303</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2439</v>
+        <v>0.624</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0276</v>
+        <v>0.2224</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2164</v>
+        <v>0.4015</v>
       </c>
       <c r="V20" t="n">
         <v>-2.8681</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5288</v>
+        <v>-5.8323</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0596</v>
+        <v>-4.5724</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4692</v>
+        <v>-1.2599</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4222</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0065</v>
+        <v>0.7029</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.291</v>
+        <v>0.1961</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2975</v>
+        <v>0.5068</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.796999999999997</v>
+        <v>8.446699999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>9.802100000000001</v>
+        <v>9.802200000000003</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0049</v>
+        <v>-1.3552</v>
       </c>
       <c r="G22" t="n">
         <v>6.311999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>14.1525</v>
       </c>
       <c r="S22" t="n">
-        <v>8.088800000000001</v>
+        <v>8.738100000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>5.472199999999999</v>
+        <v>5.472200000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>2.6165</v>
+        <v>3.2661</v>
       </c>
       <c r="V22" t="n">
         <v>-7.547099999999999</v>
